--- a/roadmap/BOB_Roadmap_Gantt.xlsx
+++ b/roadmap/BOB_Roadmap_Gantt.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Roadmap" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/roadmap/BOB_Roadmap_Gantt.xlsx
+++ b/roadmap/BOB_Roadmap_Gantt.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3808,96 +3808,98 @@
       <c r="Z58" s="6" t="n"/>
       <c r="AA58" s="6" t="n"/>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Roadmap tracker automation: CSV source + generator + Markdown + GitHub Action</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="I59" s="6" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
+      <c r="N59" s="6" t="n"/>
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="6" t="n"/>
+      <c r="Q59" s="6" t="n"/>
+      <c r="R59" s="6" t="n"/>
+      <c r="S59" s="6" t="n"/>
+      <c r="T59" s="6" t="n"/>
+      <c r="U59" s="6" t="n"/>
+      <c r="V59" s="6" t="n"/>
+      <c r="W59" s="6" t="n"/>
+      <c r="X59" s="6" t="n"/>
+      <c r="Y59" s="6" t="n"/>
+      <c r="Z59" s="6" t="n"/>
+      <c r="AA59" s="6" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>WEBSITE — REMAINING TO GO-LIVE  ·  Aug–Dec 2026</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="I59" s="7" t="n"/>
-      <c r="J59" s="7" t="n"/>
-      <c r="K59" s="7" t="n"/>
-      <c r="L59" s="7" t="n"/>
-      <c r="M59" s="7" t="n"/>
-      <c r="N59" s="7" t="n"/>
-      <c r="O59" s="7" t="n"/>
-      <c r="P59" s="7" t="n"/>
-      <c r="Q59" s="7" t="n"/>
-      <c r="R59" s="7" t="n"/>
-      <c r="S59" s="7" t="n"/>
-      <c r="T59" s="7" t="n"/>
-      <c r="U59" s="7" t="n"/>
-      <c r="V59" s="7" t="n"/>
-      <c r="W59" s="7" t="n"/>
-      <c r="X59" s="7" t="n"/>
-      <c r="Y59" s="7" t="n"/>
-      <c r="Z59" s="7" t="n"/>
-      <c r="AA59" s="7" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>Empty / error / loading states + server-side validation pass</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>46249</v>
-      </c>
-      <c r="G60" s="11" t="n">
-        <v>46295</v>
-      </c>
-      <c r="H60" s="11" t="inlineStr"/>
-      <c r="I60" s="6" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-      <c r="M60" s="6" t="n"/>
-      <c r="N60" s="6" t="n"/>
-      <c r="O60" s="6" t="n"/>
-      <c r="P60" s="6" t="n"/>
-      <c r="Q60" s="6" t="n"/>
-      <c r="R60" s="6" t="n"/>
-      <c r="S60" s="6" t="n"/>
-      <c r="T60" s="6" t="n"/>
-      <c r="U60" s="6" t="n"/>
-      <c r="V60" s="6" t="n"/>
-      <c r="W60" s="6" t="n"/>
-      <c r="X60" s="6" t="n"/>
-      <c r="Y60" s="6" t="n"/>
-      <c r="Z60" s="6" t="n"/>
-      <c r="AA60" s="6" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="7" t="n"/>
+      <c r="O60" s="7" t="n"/>
+      <c r="P60" s="7" t="n"/>
+      <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="7" t="n"/>
+      <c r="S60" s="7" t="n"/>
+      <c r="T60" s="7" t="n"/>
+      <c r="U60" s="7" t="n"/>
+      <c r="V60" s="7" t="n"/>
+      <c r="W60" s="7" t="n"/>
+      <c r="X60" s="7" t="n"/>
+      <c r="Y60" s="7" t="n"/>
+      <c r="Z60" s="7" t="n"/>
+      <c r="AA60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -3912,7 +3914,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Automated pro verification + verified badge</t>
+          <t>Empty / error / loading states + server-side validation pass</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -3921,10 +3923,10 @@
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>46266</v>
+        <v>46249</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="H61" s="11" t="inlineStr"/>
       <c r="I61" s="6" t="n"/>
@@ -3947,39 +3949,39 @@
       <c r="Z61" s="6" t="n"/>
       <c r="AA61" s="6" t="n"/>
     </row>
-    <row r="62" outlineLevel="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
-        <is>
-          <t>VIES / Agenzia Entrate P.IVA check integration</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Automated pro verification + verified badge</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F62" s="14" t="n">
+      <c r="F62" s="11" t="n">
         <v>46266</v>
       </c>
-      <c r="G62" s="14" t="n">
-        <v>46295</v>
-      </c>
-      <c r="H62" s="14" t="inlineStr"/>
+      <c r="G62" s="11" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H62" s="11" t="inlineStr"/>
       <c r="I62" s="6" t="n"/>
       <c r="J62" s="6" t="n"/>
       <c r="K62" s="6" t="n"/>
@@ -4003,22 +4005,22 @@
     <row r="63" outlineLevel="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>Internal</t>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Lucio</t>
+          <t>André</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>ID document upload + manual review queue in admin</t>
+          <t>VIES / Agenzia Entrate P.IVA check integration</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -4027,10 +4029,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>46310</v>
+        <v>46295</v>
       </c>
       <c r="H63" s="14" t="inlineStr"/>
       <c r="I63" s="6" t="n"/>
@@ -4056,22 +4058,22 @@
     <row r="64" outlineLevel="1">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>André</t>
+          <t>Lucio</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Verified badge UI on profiles, listings and ranking; 48h SLA workflow</t>
+          <t>ID document upload + manual review queue in admin</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -4080,10 +4082,10 @@
         </is>
       </c>
       <c r="F64" s="14" t="n">
-        <v>46296</v>
+        <v>46280</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="H64" s="14" t="inlineStr"/>
       <c r="I64" s="6" t="n"/>
@@ -4106,10 +4108,10 @@
       <c r="Z64" s="6" t="n"/>
       <c r="AA64" s="6" t="n"/>
     </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -4117,28 +4119,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Transparent ranking + Visibility Boost</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Verified badge UI on profiles, listings and ranking; 48h SLA workflow</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F65" s="11" t="n">
+      <c r="F65" s="14" t="n">
         <v>46296</v>
       </c>
-      <c r="G65" s="11" t="n">
-        <v>46356</v>
-      </c>
-      <c r="H65" s="11" t="inlineStr"/>
+      <c r="G65" s="14" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H65" s="14" t="inlineStr"/>
       <c r="I65" s="6" t="n"/>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="6" t="n"/>
@@ -4159,39 +4161,39 @@
       <c r="Z65" s="6" t="n"/>
       <c r="AA65" s="6" t="n"/>
     </row>
-    <row r="66" outlineLevel="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>Lucio</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>Ranking algorithm v1: response rate, closure rate, reviews (data logic)</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Transparent ranking + Visibility Boost</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F66" s="14" t="n">
+      <c r="F66" s="11" t="n">
         <v>46296</v>
       </c>
-      <c r="G66" s="14" t="n">
-        <v>46326</v>
-      </c>
-      <c r="H66" s="14" t="inlineStr"/>
+      <c r="G66" s="11" t="n">
+        <v>46356</v>
+      </c>
+      <c r="H66" s="11" t="inlineStr"/>
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="6" t="n"/>
       <c r="K66" s="6" t="n"/>
@@ -4215,22 +4217,22 @@
     <row r="67" outlineLevel="1">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>André</t>
+          <t>Lucio</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Ranking explanation UI (seeded by 'why this pro' line)</t>
+          <t>Ranking algorithm v1: response rate, closure rate, reviews (data logic)</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
@@ -4239,10 +4241,10 @@
         </is>
       </c>
       <c r="F67" s="14" t="n">
-        <v>46310</v>
+        <v>46296</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>46341</v>
+        <v>46326</v>
       </c>
       <c r="H67" s="14" t="inlineStr"/>
       <c r="I67" s="6" t="n"/>
@@ -4268,7 +4270,7 @@
     <row r="68" outlineLevel="1">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -4283,7 +4285,7 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Boost purchase + placement logic; quality floor</t>
+          <t>Ranking explanation UI (seeded by 'why this pro' line)</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -4292,10 +4294,10 @@
         </is>
       </c>
       <c r="F68" s="14" t="n">
-        <v>46327</v>
+        <v>46310</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>46356</v>
+        <v>46341</v>
       </c>
       <c r="H68" s="14" t="inlineStr"/>
       <c r="I68" s="6" t="n"/>
@@ -4318,10 +4320,10 @@
       <c r="Z68" s="6" t="n"/>
       <c r="AA68" s="6" t="n"/>
     </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -4329,28 +4331,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Stripe billing — Pro EUR24/19, Business EUR59/49</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Boost purchase + placement logic; quality floor</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F69" s="11" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G69" s="11" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H69" s="11" t="inlineStr"/>
+      <c r="F69" s="14" t="n">
+        <v>46327</v>
+      </c>
+      <c r="G69" s="14" t="n">
+        <v>46356</v>
+      </c>
+      <c r="H69" s="14" t="inlineStr"/>
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="6" t="n"/>
@@ -4371,10 +4373,10 @@
       <c r="Z69" s="6" t="n"/>
       <c r="AA69" s="6" t="n"/>
     </row>
-    <row r="70" outlineLevel="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>12.1</t>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -4382,28 +4384,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>Stripe products &amp; prices; checkout + customer portal</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Stripe billing — Pro EUR24/19, Business EUR59/49</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F70" s="14" t="n">
+      <c r="F70" s="11" t="n">
         <v>46296</v>
       </c>
-      <c r="G70" s="14" t="n">
-        <v>46356</v>
-      </c>
-      <c r="H70" s="14" t="inlineStr"/>
+      <c r="G70" s="11" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H70" s="11" t="inlineStr"/>
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="6" t="n"/>
       <c r="K70" s="6" t="n"/>
@@ -4427,12 +4429,12 @@
     <row r="71" outlineLevel="1">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -4442,7 +4444,7 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Webhooks -&gt; subscription_tier sync (replaces manual switch)</t>
+          <t>Stripe products &amp; prices; checkout + customer portal</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
@@ -4451,7 +4453,7 @@
         </is>
       </c>
       <c r="F71" s="14" t="n">
-        <v>46327</v>
+        <v>46296</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>46356</v>
@@ -4480,12 +4482,12 @@
     <row r="72" outlineLevel="1">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -4495,7 +4497,7 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>Founding-pro coupon; failed payments, invoices, receipts</t>
+          <t>Webhooks -&gt; subscription_tier sync (replaces manual switch)</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -4504,10 +4506,10 @@
         </is>
       </c>
       <c r="F72" s="14" t="n">
-        <v>46341</v>
+        <v>46327</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="H72" s="14" t="inlineStr"/>
       <c r="I72" s="6" t="n"/>
@@ -4530,10 +4532,10 @@
       <c r="Z72" s="6" t="n"/>
       <c r="AA72" s="6" t="n"/>
     </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>13</t>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>12.3</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -4541,28 +4543,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>SEO content engine (ongoing)</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F73" s="11" t="n">
-        <v>46235</v>
-      </c>
-      <c r="G73" s="11" t="n">
-        <v>46752</v>
-      </c>
-      <c r="H73" s="11" t="inlineStr"/>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Founding-pro coupon; failed payments, invoices, receipts</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>46341</v>
+      </c>
+      <c r="G73" s="14" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="6" t="n"/>
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="6" t="n"/>
@@ -4583,10 +4585,10 @@
       <c r="Z73" s="6" t="n"/>
       <c r="AA73" s="6" t="n"/>
     </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>13.1</t>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -4594,30 +4596,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>Keyword plan from Semrush data</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F74" s="14" t="n">
-        <v>46204</v>
-      </c>
-      <c r="G74" s="14" t="n">
-        <v>46208</v>
-      </c>
-      <c r="H74" s="14" t="n">
-        <v>46208</v>
-      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>SEO content engine (ongoing)</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>46235</v>
+      </c>
+      <c r="G74" s="11" t="n">
+        <v>46752</v>
+      </c>
+      <c r="H74" s="11" t="inlineStr"/>
       <c r="I74" s="6" t="n"/>
       <c r="J74" s="6" t="n"/>
       <c r="K74" s="6" t="n"/>
@@ -4641,7 +4641,7 @@
     <row r="75" outlineLevel="1">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -4656,21 +4656,23 @@
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>City x service page template + Milano core categories</t>
+          <t>Keyword plan from Semrush data</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F75" s="14" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>46326</v>
-      </c>
-      <c r="H75" s="14" t="inlineStr"/>
+        <v>46208</v>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>46208</v>
+      </c>
       <c r="I75" s="6" t="n"/>
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="6" t="n"/>
@@ -4694,7 +4696,7 @@
     <row r="76" outlineLevel="1">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -4709,7 +4711,7 @@
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>'Quanto costa' price guides; Roma+Torino pages before activation</t>
+          <t>City x service page template + Milano core categories</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -4718,10 +4720,10 @@
         </is>
       </c>
       <c r="F76" s="14" t="n">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>46477</v>
+        <v>46326</v>
       </c>
       <c r="H76" s="14" t="inlineStr"/>
       <c r="I76" s="6" t="n"/>
@@ -4744,35 +4746,39 @@
       <c r="Z76" s="6" t="n"/>
       <c r="AA76" s="6" t="n"/>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr"/>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Google Business Profile + local presence</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>'Quanto costa' price guides; Roma+Torino pages before activation</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F77" s="11" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G77" s="11" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H77" s="11" t="inlineStr"/>
+      <c r="F77" s="14" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G77" s="14" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H77" s="14" t="inlineStr"/>
       <c r="I77" s="6" t="n"/>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="6" t="n"/>
@@ -4796,7 +4802,7 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
@@ -4807,7 +4813,7 @@
       <c r="C78" s="8" t="inlineStr"/>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Launch hardening</t>
+          <t>Google Business Profile + local presence</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -4816,7 +4822,7 @@
         </is>
       </c>
       <c r="F78" s="11" t="n">
-        <v>46357</v>
+        <v>46327</v>
       </c>
       <c r="G78" s="11" t="n">
         <v>46387</v>
@@ -4842,10 +4848,10 @@
       <c r="Z78" s="6" t="n"/>
       <c r="AA78" s="6" t="n"/>
     </row>
-    <row r="79" outlineLevel="1">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>15.1</t>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
@@ -4853,24 +4859,24 @@
           <t>Shared</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr"/>
-      <c r="D79" s="13" t="inlineStr">
-        <is>
-          <t>End-to-end QA of all flows (client, pro, admin)</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr"/>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Launch hardening</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F79" s="14" t="n">
+      <c r="F79" s="11" t="n">
         <v>46357</v>
       </c>
-      <c r="G79" s="14" t="n">
-        <v>46371</v>
-      </c>
-      <c r="H79" s="14" t="inlineStr"/>
+      <c r="G79" s="11" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H79" s="11" t="inlineStr"/>
       <c r="I79" s="6" t="n"/>
       <c r="J79" s="6" t="n"/>
       <c r="K79" s="6" t="n"/>
@@ -4894,22 +4900,18 @@
     <row r="80" outlineLevel="1">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr"/>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>Performance / Core Web Vitals pass</t>
+          <t>End-to-end QA of all flows (client, pro, admin)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -4921,7 +4923,7 @@
         <v>46357</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>46376</v>
+        <v>46371</v>
       </c>
       <c r="H80" s="14" t="inlineStr"/>
       <c r="I80" s="6" t="n"/>
@@ -4947,18 +4949,22 @@
     <row r="81" outlineLevel="1">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr"/>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Freelance security review (pre-launch)</t>
+          <t>Performance / Core Web Vitals pass</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -4996,22 +5002,18 @@
     <row r="82" outlineLevel="1">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr"/>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Activate email notifications (Resend): account, DNS/DKIM, env vars, deliverability test</t>
+          <t>Freelance security review (pre-launch)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -5049,22 +5051,22 @@
     <row r="83" outlineLevel="1">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>Internal</t>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Lucio</t>
+          <t>André</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Error monitoring, uptime alerts, backups; go-live checklist + rollback</t>
+          <t>Activate email notifications (Resend): account, DNS/DKIM, env vars, deliverability test</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -5073,10 +5075,10 @@
         </is>
       </c>
       <c r="F83" s="14" t="n">
-        <v>46366</v>
+        <v>46357</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>46387</v>
+        <v>46376</v>
       </c>
       <c r="H83" s="14" t="inlineStr"/>
       <c r="I83" s="6" t="n"/>
@@ -5099,41 +5101,39 @@
       <c r="Z83" s="6" t="n"/>
       <c r="AA83" s="6" t="n"/>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>Bx</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>Email notifications pipeline — BUILT, DORMANT (activates with RESEND_API_KEY)</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="n">
-        <v>46222</v>
-      </c>
-      <c r="G84" s="11" t="n">
-        <v>46222</v>
-      </c>
-      <c r="H84" s="11" t="n">
-        <v>46222</v>
-      </c>
+    <row r="84" outlineLevel="1">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Lucio</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>Error monitoring, uptime alerts, backups; go-live checklist + rollback</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>46366</v>
+      </c>
+      <c r="G84" s="14" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H84" s="14" t="inlineStr"/>
       <c r="I84" s="6" t="n"/>
       <c r="J84" s="6" t="n"/>
       <c r="K84" s="6" t="n"/>
@@ -5154,117 +5154,123 @@
       <c r="Z84" s="6" t="n"/>
       <c r="AA84" s="6" t="n"/>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>Bx</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Email notifications pipeline — BUILT, DORMANT (activates with RESEND_API_KEY)</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="G85" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="H85" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="I85" s="6" t="n"/>
+      <c r="J85" s="6" t="n"/>
+      <c r="K85" s="6" t="n"/>
+      <c r="L85" s="6" t="n"/>
+      <c r="M85" s="6" t="n"/>
+      <c r="N85" s="6" t="n"/>
+      <c r="O85" s="6" t="n"/>
+      <c r="P85" s="6" t="n"/>
+      <c r="Q85" s="6" t="n"/>
+      <c r="R85" s="6" t="n"/>
+      <c r="S85" s="6" t="n"/>
+      <c r="T85" s="6" t="n"/>
+      <c r="U85" s="6" t="n"/>
+      <c r="V85" s="6" t="n"/>
+      <c r="W85" s="6" t="n"/>
+      <c r="X85" s="6" t="n"/>
+      <c r="Y85" s="6" t="n"/>
+      <c r="Z85" s="6" t="n"/>
+      <c r="AA85" s="6" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>LAUNCH &amp; YEAR-1 PRODUCT  ·  2027</t>
         </is>
       </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="6" t="n"/>
-      <c r="I85" s="7" t="n"/>
-      <c r="J85" s="7" t="n"/>
-      <c r="K85" s="7" t="n"/>
-      <c r="L85" s="7" t="n"/>
-      <c r="M85" s="7" t="n"/>
-      <c r="N85" s="7" t="n"/>
-      <c r="O85" s="7" t="n"/>
-      <c r="P85" s="7" t="n"/>
-      <c r="Q85" s="7" t="n"/>
-      <c r="R85" s="7" t="n"/>
-      <c r="S85" s="7" t="n"/>
-      <c r="T85" s="7" t="n"/>
-      <c r="U85" s="7" t="n"/>
-      <c r="V85" s="7" t="n"/>
-      <c r="W85" s="7" t="n"/>
-      <c r="X85" s="7" t="n"/>
-      <c r="Y85" s="7" t="n"/>
-      <c r="Z85" s="7" t="n"/>
-      <c r="AA85" s="7" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="6" t="n"/>
+      <c r="I86" s="7" t="n"/>
+      <c r="J86" s="7" t="n"/>
+      <c r="K86" s="7" t="n"/>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
+      <c r="N86" s="7" t="n"/>
+      <c r="O86" s="7" t="n"/>
+      <c r="P86" s="7" t="n"/>
+      <c r="Q86" s="7" t="n"/>
+      <c r="R86" s="7" t="n"/>
+      <c r="S86" s="7" t="n"/>
+      <c r="T86" s="7" t="n"/>
+      <c r="U86" s="7" t="n"/>
+      <c r="V86" s="7" t="n"/>
+      <c r="W86" s="7" t="n"/>
+      <c r="X86" s="7" t="n"/>
+      <c r="Y86" s="7" t="n"/>
+      <c r="Z86" s="7" t="n"/>
+      <c r="AA86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr"/>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr"/>
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>GO-LIVE — Milano pilot</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="F86" s="11" t="n">
+      <c r="F87" s="11" t="n">
         <v>46388</v>
       </c>
-      <c r="G86" s="11" t="n">
+      <c r="G87" s="11" t="n">
         <v>46418</v>
       </c>
-      <c r="H86" s="11" t="inlineStr"/>
-      <c r="I86" s="6" t="n"/>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="6" t="n"/>
-      <c r="L86" s="6" t="n"/>
-      <c r="M86" s="6" t="n"/>
-      <c r="N86" s="6" t="n"/>
-      <c r="O86" s="6" t="n"/>
-      <c r="P86" s="6" t="n"/>
-      <c r="Q86" s="6" t="n"/>
-      <c r="R86" s="6" t="n"/>
-      <c r="S86" s="6" t="n"/>
-      <c r="T86" s="6" t="n"/>
-      <c r="U86" s="6" t="n"/>
-      <c r="V86" s="6" t="n"/>
-      <c r="W86" s="6" t="n"/>
-      <c r="X86" s="6" t="n"/>
-      <c r="Y86" s="6" t="n"/>
-      <c r="Z86" s="6" t="n"/>
-      <c r="AA86" s="6" t="n"/>
-    </row>
-    <row r="87" outlineLevel="1">
-      <c r="A87" s="12" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B87" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="inlineStr"/>
-      <c r="D87" s="13" t="inlineStr">
-        <is>
-          <t>Production cutover; activate founding pros (60-80) in 5 core categories</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>46388</v>
-      </c>
-      <c r="G87" s="14" t="n">
-        <v>46418</v>
-      </c>
-      <c r="H87" s="14" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="6" t="n"/>
       <c r="J87" s="6" t="n"/>
       <c r="K87" s="6" t="n"/>
@@ -5288,7 +5294,7 @@
     <row r="88" outlineLevel="1">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
@@ -5299,7 +5305,7 @@
       <c r="C88" s="12" t="inlineStr"/>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>Bob Pro subscriptions live (Stripe) + Boost on; launch PR wave</t>
+          <t>Production cutover; activate founding pros (60-80) in 5 core categories</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -5334,39 +5340,35 @@
       <c r="Z88" s="6" t="n"/>
       <c r="AA88" s="6" t="n"/>
     </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>Unlimited requests (subscribers) + digital quotes</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
+    <row r="89" outlineLevel="1">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr"/>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>Bob Pro subscriptions live (Stripe) + Boost on; launch PR wave</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F89" s="11" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G89" s="11" t="n">
-        <v>46568</v>
-      </c>
-      <c r="H89" s="11" t="inlineStr"/>
+      <c r="F89" s="14" t="n">
+        <v>46388</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>46418</v>
+      </c>
+      <c r="H89" s="14" t="inlineStr"/>
       <c r="I89" s="6" t="n"/>
       <c r="J89" s="6" t="n"/>
       <c r="K89" s="6" t="n"/>
@@ -5387,10 +5389,10 @@
       <c r="Z89" s="6" t="n"/>
       <c r="AA89" s="6" t="n"/>
     </row>
-    <row r="90" outlineLevel="1">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>17.1</t>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -5398,28 +5400,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>Free-tier request limits + upgrade paywall</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Unlimited requests (subscribers) + digital quotes</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F90" s="14" t="n">
+      <c r="F90" s="11" t="n">
         <v>46447</v>
       </c>
-      <c r="G90" s="14" t="n">
-        <v>46492</v>
-      </c>
-      <c r="H90" s="14" t="inlineStr"/>
+      <c r="G90" s="11" t="n">
+        <v>46568</v>
+      </c>
+      <c r="H90" s="11" t="inlineStr"/>
       <c r="I90" s="6" t="n"/>
       <c r="J90" s="6" t="n"/>
       <c r="K90" s="6" t="n"/>
@@ -5443,7 +5445,7 @@
     <row r="91" outlineLevel="1">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -5458,7 +5460,7 @@
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Quote builder for pros + client quote comparison + accept flow</t>
+          <t>Free-tier request limits + upgrade paywall</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -5467,10 +5469,10 @@
         </is>
       </c>
       <c r="F91" s="14" t="n">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>46568</v>
+        <v>46492</v>
       </c>
       <c r="H91" s="14" t="inlineStr"/>
       <c r="I91" s="6" t="n"/>
@@ -5493,35 +5495,39 @@
       <c r="Z91" s="6" t="n"/>
       <c r="AA91" s="6" t="n"/>
     </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr"/>
-      <c r="D92" s="10" t="inlineStr">
-        <is>
-          <t>Security audit (gate before payments)</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
+    <row r="92" outlineLevel="1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>Quote builder for pros + client quote comparison + accept flow</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F92" s="11" t="n">
-        <v>46539</v>
-      </c>
-      <c r="G92" s="11" t="n">
-        <v>46599</v>
-      </c>
-      <c r="H92" s="11" t="inlineStr"/>
+      <c r="F92" s="14" t="n">
+        <v>46478</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>46568</v>
+      </c>
+      <c r="H92" s="14" t="inlineStr"/>
       <c r="I92" s="6" t="n"/>
       <c r="J92" s="6" t="n"/>
       <c r="K92" s="6" t="n"/>
@@ -5545,22 +5551,18 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>Client/Pro</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr"/>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Protected flow — payments + Garanzia Bob</t>
+          <t>Security audit (gate before payments)</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -5569,10 +5571,10 @@
         </is>
       </c>
       <c r="F93" s="11" t="n">
-        <v>46569</v>
+        <v>46539</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>46752</v>
+        <v>46599</v>
       </c>
       <c r="H93" s="11" t="inlineStr"/>
       <c r="I93" s="6" t="n"/>
@@ -5595,10 +5597,10 @@
       <c r="Z93" s="6" t="n"/>
       <c r="AA93" s="6" t="n"/>
     </row>
-    <row r="94" outlineLevel="1">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>19.1</t>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -5606,28 +5608,28 @@
           <t>Client/Pro</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>André</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
-        <is>
-          <t>Stripe Connect: deposit/escrow, payouts; dispute + mediation tooling</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Protected flow — payments + Garanzia Bob</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F94" s="14" t="n">
+      <c r="F94" s="11" t="n">
         <v>46569</v>
       </c>
-      <c r="G94" s="14" t="n">
-        <v>46691</v>
-      </c>
-      <c r="H94" s="14" t="inlineStr"/>
+      <c r="G94" s="11" t="n">
+        <v>46752</v>
+      </c>
+      <c r="H94" s="11" t="inlineStr"/>
       <c r="I94" s="6" t="n"/>
       <c r="J94" s="6" t="n"/>
       <c r="K94" s="6" t="n"/>
@@ -5651,7 +5653,7 @@
     <row r="95" outlineLevel="1">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -5666,7 +5668,7 @@
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Verified reviews tied to protected jobs; 8% success fee billing</t>
+          <t>Stripe Connect: deposit/escrow, payouts; dispute + mediation tooling</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
@@ -5675,10 +5677,10 @@
         </is>
       </c>
       <c r="F95" s="14" t="n">
-        <v>46645</v>
+        <v>46569</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>46706</v>
+        <v>46691</v>
       </c>
       <c r="H95" s="14" t="inlineStr"/>
       <c r="I95" s="6" t="n"/>
@@ -5701,35 +5703,39 @@
       <c r="Z95" s="6" t="n"/>
       <c r="AA95" s="6" t="n"/>
     </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr"/>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>Roma + Torino activation</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
+    <row r="96" outlineLevel="1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Client/Pro</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>Verified reviews tied to protected jobs; 8% success fee billing</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F96" s="11" t="n">
-        <v>46478</v>
-      </c>
-      <c r="G96" s="11" t="n">
-        <v>46568</v>
-      </c>
-      <c r="H96" s="11" t="inlineStr"/>
+      <c r="F96" s="14" t="n">
+        <v>46645</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <v>46706</v>
+      </c>
+      <c r="H96" s="14" t="inlineStr"/>
       <c r="I96" s="6" t="n"/>
       <c r="J96" s="6" t="n"/>
       <c r="K96" s="6" t="n"/>
@@ -5753,7 +5759,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
@@ -5764,7 +5770,7 @@
       <c r="C97" s="8" t="inlineStr"/>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Bologna, Firenze, Napoli activation</t>
+          <t>Roma + Torino activation</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -5773,10 +5779,10 @@
         </is>
       </c>
       <c r="F97" s="11" t="n">
-        <v>46569</v>
+        <v>46478</v>
       </c>
       <c r="G97" s="11" t="n">
-        <v>46752</v>
+        <v>46568</v>
       </c>
       <c r="H97" s="11" t="inlineStr"/>
       <c r="I97" s="6" t="n"/>
@@ -5802,7 +5808,7 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
@@ -5813,7 +5819,7 @@
       <c r="C98" s="8" t="inlineStr"/>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>National infrastructural opening (organic only)</t>
+          <t>Bologna, Firenze, Napoli activation</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -5822,7 +5828,7 @@
         </is>
       </c>
       <c r="F98" s="11" t="n">
-        <v>46661</v>
+        <v>46569</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>46752</v>
@@ -5848,92 +5854,92 @@
       <c r="Z98" s="6" t="n"/>
       <c r="AA98" s="6" t="n"/>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr"/>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>National infrastructural opening (organic only)</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>46661</v>
+      </c>
+      <c r="G99" s="11" t="n">
+        <v>46752</v>
+      </c>
+      <c r="H99" s="11" t="inlineStr"/>
+      <c r="I99" s="6" t="n"/>
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="6" t="n"/>
+      <c r="L99" s="6" t="n"/>
+      <c r="M99" s="6" t="n"/>
+      <c r="N99" s="6" t="n"/>
+      <c r="O99" s="6" t="n"/>
+      <c r="P99" s="6" t="n"/>
+      <c r="Q99" s="6" t="n"/>
+      <c r="R99" s="6" t="n"/>
+      <c r="S99" s="6" t="n"/>
+      <c r="T99" s="6" t="n"/>
+      <c r="U99" s="6" t="n"/>
+      <c r="V99" s="6" t="n"/>
+      <c r="W99" s="6" t="n"/>
+      <c r="X99" s="6" t="n"/>
+      <c r="Y99" s="6" t="n"/>
+      <c r="Z99" s="6" t="n"/>
+      <c r="AA99" s="6" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>LEGAL &amp; BUREAUCRACY</t>
         </is>
       </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="6" t="n"/>
-      <c r="I99" s="7" t="n"/>
-      <c r="J99" s="7" t="n"/>
-      <c r="K99" s="7" t="n"/>
-      <c r="L99" s="7" t="n"/>
-      <c r="M99" s="7" t="n"/>
-      <c r="N99" s="7" t="n"/>
-      <c r="O99" s="7" t="n"/>
-      <c r="P99" s="7" t="n"/>
-      <c r="Q99" s="7" t="n"/>
-      <c r="R99" s="7" t="n"/>
-      <c r="S99" s="7" t="n"/>
-      <c r="T99" s="7" t="n"/>
-      <c r="U99" s="7" t="n"/>
-      <c r="V99" s="7" t="n"/>
-      <c r="W99" s="7" t="n"/>
-      <c r="X99" s="7" t="n"/>
-      <c r="Y99" s="7" t="n"/>
-      <c r="Z99" s="7" t="n"/>
-      <c r="AA99" s="7" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>Site legal docs (ToS, privacy, cookie + consent banner) + lawyer review</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F100" s="11" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G100" s="11" t="n">
-        <v>46356</v>
-      </c>
-      <c r="H100" s="11" t="inlineStr"/>
-      <c r="I100" s="6" t="n"/>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="6" t="n"/>
-      <c r="L100" s="6" t="n"/>
-      <c r="M100" s="6" t="n"/>
-      <c r="N100" s="6" t="n"/>
-      <c r="O100" s="6" t="n"/>
-      <c r="P100" s="6" t="n"/>
-      <c r="Q100" s="6" t="n"/>
-      <c r="R100" s="6" t="n"/>
-      <c r="S100" s="6" t="n"/>
-      <c r="T100" s="6" t="n"/>
-      <c r="U100" s="6" t="n"/>
-      <c r="V100" s="6" t="n"/>
-      <c r="W100" s="6" t="n"/>
-      <c r="X100" s="6" t="n"/>
-      <c r="Y100" s="6" t="n"/>
-      <c r="Z100" s="6" t="n"/>
-      <c r="AA100" s="6" t="n"/>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="6" t="n"/>
+      <c r="G100" s="6" t="n"/>
+      <c r="H100" s="6" t="n"/>
+      <c r="I100" s="7" t="n"/>
+      <c r="J100" s="7" t="n"/>
+      <c r="K100" s="7" t="n"/>
+      <c r="L100" s="7" t="n"/>
+      <c r="M100" s="7" t="n"/>
+      <c r="N100" s="7" t="n"/>
+      <c r="O100" s="7" t="n"/>
+      <c r="P100" s="7" t="n"/>
+      <c r="Q100" s="7" t="n"/>
+      <c r="R100" s="7" t="n"/>
+      <c r="S100" s="7" t="n"/>
+      <c r="T100" s="7" t="n"/>
+      <c r="U100" s="7" t="n"/>
+      <c r="V100" s="7" t="n"/>
+      <c r="W100" s="7" t="n"/>
+      <c r="X100" s="7" t="n"/>
+      <c r="Y100" s="7" t="n"/>
+      <c r="Z100" s="7" t="n"/>
+      <c r="AA100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B101" s="16" t="inlineStr">
@@ -5944,7 +5950,7 @@
       <c r="C101" s="8" t="inlineStr"/>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Trademark 'Bob' (UIBM/EUIPO, classes 35, 42)</t>
+          <t>Site legal docs (ToS, privacy, cookie + consent banner) + lawyer review</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -5956,7 +5962,7 @@
         <v>46266</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="H101" s="11" t="inlineStr"/>
       <c r="I101" s="6" t="n"/>
@@ -5982,7 +5988,7 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
@@ -5993,7 +5999,7 @@
       <c r="C102" s="8" t="inlineStr"/>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>GDPR full compliance</t>
+          <t>Trademark 'Bob' (UIBM/EUIPO, classes 35, 42)</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -6002,10 +6008,10 @@
         </is>
       </c>
       <c r="F102" s="11" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>46418</v>
+        <v>46326</v>
       </c>
       <c r="H102" s="11" t="inlineStr"/>
       <c r="I102" s="6" t="n"/>
@@ -6028,39 +6034,35 @@
       <c r="Z102" s="6" t="n"/>
       <c r="AA102" s="6" t="n"/>
     </row>
-    <row r="103" outlineLevel="1">
-      <c r="A103" s="12" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>Lucio</t>
-        </is>
-      </c>
-      <c r="D103" s="13" t="inlineStr">
-        <is>
-          <t>Registro trattamenti + retention policy; consent flows audit; breach procedure</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr"/>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>GDPR full compliance</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F103" s="14" t="n">
+      <c r="F103" s="11" t="n">
         <v>46327</v>
       </c>
-      <c r="G103" s="14" t="n">
+      <c r="G103" s="11" t="n">
         <v>46418</v>
       </c>
-      <c r="H103" s="14" t="inlineStr"/>
+      <c r="H103" s="11" t="inlineStr"/>
       <c r="I103" s="6" t="n"/>
       <c r="J103" s="6" t="n"/>
       <c r="K103" s="6" t="n"/>
@@ -6084,18 +6086,22 @@
     <row r="104" outlineLevel="1">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr"/>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Lucio</t>
+        </is>
+      </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>DPAs with processors (Supabase, Vercel, Anthropic, Stripe, Resend)</t>
+          <t>Registro trattamenti + retention policy; consent flows audit; breach procedure</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -6104,10 +6110,10 @@
         </is>
       </c>
       <c r="F104" s="14" t="n">
-        <v>46341</v>
+        <v>46327</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="H104" s="14" t="inlineStr"/>
       <c r="I104" s="6" t="n"/>
@@ -6130,10 +6136,10 @@
       <c r="Z104" s="6" t="n"/>
       <c r="AA104" s="6" t="n"/>
     </row>
-    <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>26</t>
+    <row r="105" outlineLevel="1">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>25.2</t>
         </is>
       </c>
       <c r="B105" s="16" t="inlineStr">
@@ -6141,24 +6147,24 @@
           <t>Shared</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr"/>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>SRL incorporation (Q1 Year 1)</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr"/>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>DPAs with processors (Supabase, Vercel, Anthropic, Stripe, Resend)</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F105" s="11" t="n">
-        <v>46357</v>
-      </c>
-      <c r="G105" s="11" t="n">
-        <v>46446</v>
-      </c>
-      <c r="H105" s="11" t="inlineStr"/>
+      <c r="F105" s="14" t="n">
+        <v>46341</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H105" s="14" t="inlineStr"/>
       <c r="I105" s="6" t="n"/>
       <c r="J105" s="6" t="n"/>
       <c r="K105" s="6" t="n"/>
@@ -6182,7 +6188,7 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
@@ -6193,7 +6199,7 @@
       <c r="C106" s="8" t="inlineStr"/>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Finanza agevolata application (Q2 Year 1)</t>
+          <t>SRL incorporation (Q1 Year 1)</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -6202,10 +6208,10 @@
         </is>
       </c>
       <c r="F106" s="11" t="n">
-        <v>46478</v>
+        <v>46357</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>46568</v>
+        <v>46446</v>
       </c>
       <c r="H106" s="11" t="inlineStr"/>
       <c r="I106" s="6" t="n"/>
@@ -6231,7 +6237,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B107" s="16" t="inlineStr">
@@ -6242,7 +6248,7 @@
       <c r="C107" s="8" t="inlineStr"/>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Garanzia Bob legal framework + payments compliance (Stripe Connect KYC)</t>
+          <t>Finanza agevolata application (Q2 Year 1)</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -6251,10 +6257,10 @@
         </is>
       </c>
       <c r="F107" s="11" t="n">
-        <v>46508</v>
+        <v>46478</v>
       </c>
       <c r="G107" s="11" t="n">
-        <v>46660</v>
+        <v>46568</v>
       </c>
       <c r="H107" s="11" t="inlineStr"/>
       <c r="I107" s="6" t="n"/>
@@ -6277,92 +6283,92 @@
       <c r="Z107" s="6" t="n"/>
       <c r="AA107" s="6" t="n"/>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr"/>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Garanzia Bob legal framework + payments compliance (Stripe Connect KYC)</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>46508</v>
+      </c>
+      <c r="G108" s="11" t="n">
+        <v>46660</v>
+      </c>
+      <c r="H108" s="11" t="inlineStr"/>
+      <c r="I108" s="6" t="n"/>
+      <c r="J108" s="6" t="n"/>
+      <c r="K108" s="6" t="n"/>
+      <c r="L108" s="6" t="n"/>
+      <c r="M108" s="6" t="n"/>
+      <c r="N108" s="6" t="n"/>
+      <c r="O108" s="6" t="n"/>
+      <c r="P108" s="6" t="n"/>
+      <c r="Q108" s="6" t="n"/>
+      <c r="R108" s="6" t="n"/>
+      <c r="S108" s="6" t="n"/>
+      <c r="T108" s="6" t="n"/>
+      <c r="U108" s="6" t="n"/>
+      <c r="V108" s="6" t="n"/>
+      <c r="W108" s="6" t="n"/>
+      <c r="X108" s="6" t="n"/>
+      <c r="Y108" s="6" t="n"/>
+      <c r="Z108" s="6" t="n"/>
+      <c r="AA108" s="6" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>GO-TO-MARKET &amp; MARKETING</t>
         </is>
       </c>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="6" t="n"/>
-      <c r="H108" s="6" t="n"/>
-      <c r="I108" s="7" t="n"/>
-      <c r="J108" s="7" t="n"/>
-      <c r="K108" s="7" t="n"/>
-      <c r="L108" s="7" t="n"/>
-      <c r="M108" s="7" t="n"/>
-      <c r="N108" s="7" t="n"/>
-      <c r="O108" s="7" t="n"/>
-      <c r="P108" s="7" t="n"/>
-      <c r="Q108" s="7" t="n"/>
-      <c r="R108" s="7" t="n"/>
-      <c r="S108" s="7" t="n"/>
-      <c r="T108" s="7" t="n"/>
-      <c r="U108" s="7" t="n"/>
-      <c r="V108" s="7" t="n"/>
-      <c r="W108" s="7" t="n"/>
-      <c r="X108" s="7" t="n"/>
-      <c r="Y108" s="7" t="n"/>
-      <c r="Z108" s="7" t="n"/>
-      <c r="AA108" s="7" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr"/>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>Founder outreach — first 100 Milano pros</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F109" s="11" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G109" s="11" t="n">
-        <v>46477</v>
-      </c>
-      <c r="H109" s="11" t="inlineStr"/>
-      <c r="I109" s="6" t="n"/>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="6" t="n"/>
-      <c r="L109" s="6" t="n"/>
-      <c r="M109" s="6" t="n"/>
-      <c r="N109" s="6" t="n"/>
-      <c r="O109" s="6" t="n"/>
-      <c r="P109" s="6" t="n"/>
-      <c r="Q109" s="6" t="n"/>
-      <c r="R109" s="6" t="n"/>
-      <c r="S109" s="6" t="n"/>
-      <c r="T109" s="6" t="n"/>
-      <c r="U109" s="6" t="n"/>
-      <c r="V109" s="6" t="n"/>
-      <c r="W109" s="6" t="n"/>
-      <c r="X109" s="6" t="n"/>
-      <c r="Y109" s="6" t="n"/>
-      <c r="Z109" s="6" t="n"/>
-      <c r="AA109" s="6" t="n"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="6" t="n"/>
+      <c r="G109" s="6" t="n"/>
+      <c r="H109" s="6" t="n"/>
+      <c r="I109" s="7" t="n"/>
+      <c r="J109" s="7" t="n"/>
+      <c r="K109" s="7" t="n"/>
+      <c r="L109" s="7" t="n"/>
+      <c r="M109" s="7" t="n"/>
+      <c r="N109" s="7" t="n"/>
+      <c r="O109" s="7" t="n"/>
+      <c r="P109" s="7" t="n"/>
+      <c r="Q109" s="7" t="n"/>
+      <c r="R109" s="7" t="n"/>
+      <c r="S109" s="7" t="n"/>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
+      <c r="W109" s="7" t="n"/>
+      <c r="X109" s="7" t="n"/>
+      <c r="Y109" s="7" t="n"/>
+      <c r="Z109" s="7" t="n"/>
+      <c r="AA109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
@@ -6373,7 +6379,7 @@
       <c r="C110" s="8" t="inlineStr"/>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Launch incentives (3 months free Bob Pro for founding pros)</t>
+          <t>Founder outreach — first 100 Milano pros</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -6382,7 +6388,7 @@
         </is>
       </c>
       <c r="F110" s="11" t="n">
-        <v>46388</v>
+        <v>46296</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>46477</v>
@@ -6411,7 +6417,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B111" s="16" t="inlineStr">
@@ -6422,7 +6428,7 @@
       <c r="C111" s="8" t="inlineStr"/>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Paid ads ignition — Milano only (CAC &lt; EUR25 Q1)</t>
+          <t>Launch incentives (3 months free Bob Pro for founding pros)</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -6434,7 +6440,7 @@
         <v>46388</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>46568</v>
+        <v>46477</v>
       </c>
       <c r="H111" s="11" t="inlineStr"/>
       <c r="I111" s="6" t="n"/>
@@ -6460,7 +6466,7 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
@@ -6471,7 +6477,7 @@
       <c r="C112" s="8" t="inlineStr"/>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>PR launch ('AI concierge that fights lavoro nero')</t>
+          <t>Paid ads ignition — Milano only (CAC &lt; EUR25 Q1)</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -6483,7 +6489,7 @@
         <v>46388</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>46477</v>
+        <v>46568</v>
       </c>
       <c r="H112" s="11" t="inlineStr"/>
       <c r="I112" s="6" t="n"/>
@@ -6509,7 +6515,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B113" s="16" t="inlineStr">
@@ -6520,7 +6526,7 @@
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Pro referral program + territorial partnerships</t>
+          <t>PR launch ('AI concierge that fights lavoro nero')</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -6529,10 +6535,10 @@
         </is>
       </c>
       <c r="F113" s="11" t="n">
-        <v>46447</v>
+        <v>46388</v>
       </c>
       <c r="G113" s="11" t="n">
-        <v>46752</v>
+        <v>46477</v>
       </c>
       <c r="H113" s="11" t="inlineStr"/>
       <c r="I113" s="6" t="n"/>
@@ -6555,96 +6561,92 @@
       <c r="Z113" s="6" t="n"/>
       <c r="AA113" s="6" t="n"/>
     </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr"/>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>Pro referral program + territorial partnerships</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G114" s="11" t="n">
+        <v>46752</v>
+      </c>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="6" t="n"/>
+      <c r="J114" s="6" t="n"/>
+      <c r="K114" s="6" t="n"/>
+      <c r="L114" s="6" t="n"/>
+      <c r="M114" s="6" t="n"/>
+      <c r="N114" s="6" t="n"/>
+      <c r="O114" s="6" t="n"/>
+      <c r="P114" s="6" t="n"/>
+      <c r="Q114" s="6" t="n"/>
+      <c r="R114" s="6" t="n"/>
+      <c r="S114" s="6" t="n"/>
+      <c r="T114" s="6" t="n"/>
+      <c r="U114" s="6" t="n"/>
+      <c r="V114" s="6" t="n"/>
+      <c r="W114" s="6" t="n"/>
+      <c r="X114" s="6" t="n"/>
+      <c r="Y114" s="6" t="n"/>
+      <c r="Z114" s="6" t="n"/>
+      <c r="AA114" s="6" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>KPI GATES  (decision checkpoints)</t>
         </is>
       </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="6" t="n"/>
-      <c r="I114" s="7" t="n"/>
-      <c r="J114" s="7" t="n"/>
-      <c r="K114" s="7" t="n"/>
-      <c r="L114" s="7" t="n"/>
-      <c r="M114" s="7" t="n"/>
-      <c r="N114" s="7" t="n"/>
-      <c r="O114" s="7" t="n"/>
-      <c r="P114" s="7" t="n"/>
-      <c r="Q114" s="7" t="n"/>
-      <c r="R114" s="7" t="n"/>
-      <c r="S114" s="7" t="n"/>
-      <c r="T114" s="7" t="n"/>
-      <c r="U114" s="7" t="n"/>
-      <c r="V114" s="7" t="n"/>
-      <c r="W114" s="7" t="n"/>
-      <c r="X114" s="7" t="n"/>
-      <c r="Y114" s="7" t="n"/>
-      <c r="Z114" s="7" t="n"/>
-      <c r="AA114" s="7" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B115" s="15" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>Lucio</t>
-        </is>
-      </c>
-      <c r="D115" s="10" t="inlineStr">
-        <is>
-          <t>End-Q1 2027: 60-80 active pros, 150+ req/mo, match &gt;60%</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="F115" s="11" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G115" s="11" t="n">
-        <v>46477</v>
-      </c>
-      <c r="H115" s="11" t="inlineStr"/>
-      <c r="I115" s="6" t="n"/>
-      <c r="J115" s="6" t="n"/>
-      <c r="K115" s="6" t="n"/>
-      <c r="L115" s="6" t="n"/>
-      <c r="M115" s="6" t="n"/>
-      <c r="N115" s="6" t="n"/>
-      <c r="O115" s="6" t="n"/>
-      <c r="P115" s="6" t="n"/>
-      <c r="Q115" s="6" t="n"/>
-      <c r="R115" s="6" t="n"/>
-      <c r="S115" s="6" t="n"/>
-      <c r="T115" s="6" t="n"/>
-      <c r="U115" s="6" t="n"/>
-      <c r="V115" s="6" t="n"/>
-      <c r="W115" s="6" t="n"/>
-      <c r="X115" s="6" t="n"/>
-      <c r="Y115" s="6" t="n"/>
-      <c r="Z115" s="6" t="n"/>
-      <c r="AA115" s="6" t="n"/>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="6" t="n"/>
+      <c r="F115" s="6" t="n"/>
+      <c r="G115" s="6" t="n"/>
+      <c r="H115" s="6" t="n"/>
+      <c r="I115" s="7" t="n"/>
+      <c r="J115" s="7" t="n"/>
+      <c r="K115" s="7" t="n"/>
+      <c r="L115" s="7" t="n"/>
+      <c r="M115" s="7" t="n"/>
+      <c r="N115" s="7" t="n"/>
+      <c r="O115" s="7" t="n"/>
+      <c r="P115" s="7" t="n"/>
+      <c r="Q115" s="7" t="n"/>
+      <c r="R115" s="7" t="n"/>
+      <c r="S115" s="7" t="n"/>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
+      <c r="W115" s="7" t="n"/>
+      <c r="X115" s="7" t="n"/>
+      <c r="Y115" s="7" t="n"/>
+      <c r="Z115" s="7" t="n"/>
+      <c r="AA115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -6659,7 +6661,7 @@
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>End-2027: 600 pros, 1,500 req/mo, 25% protected-flow, CAC &lt; EUR15</t>
+          <t>End-Q1 2027: 60-80 active pros, 150+ req/mo, match &gt;60%</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -6668,10 +6670,10 @@
         </is>
       </c>
       <c r="F116" s="11" t="n">
-        <v>46722</v>
+        <v>46447</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>46752</v>
+        <v>46477</v>
       </c>
       <c r="H116" s="11" t="inlineStr"/>
       <c r="I116" s="6" t="n"/>
@@ -6694,90 +6696,143 @@
       <c r="Z116" s="6" t="n"/>
       <c r="AA116" s="6" t="n"/>
     </row>
-    <row r="118">
-      <c r="B118" s="17" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Lucio</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>End-2027: 600 pros, 1,500 req/mo, 25% protected-flow, CAC &lt; EUR15</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G117" s="11" t="n">
+        <v>46752</v>
+      </c>
+      <c r="H117" s="11" t="inlineStr"/>
+      <c r="I117" s="6" t="n"/>
+      <c r="J117" s="6" t="n"/>
+      <c r="K117" s="6" t="n"/>
+      <c r="L117" s="6" t="n"/>
+      <c r="M117" s="6" t="n"/>
+      <c r="N117" s="6" t="n"/>
+      <c r="O117" s="6" t="n"/>
+      <c r="P117" s="6" t="n"/>
+      <c r="Q117" s="6" t="n"/>
+      <c r="R117" s="6" t="n"/>
+      <c r="S117" s="6" t="n"/>
+      <c r="T117" s="6" t="n"/>
+      <c r="U117" s="6" t="n"/>
+      <c r="V117" s="6" t="n"/>
+      <c r="W117" s="6" t="n"/>
+      <c r="X117" s="6" t="n"/>
+      <c r="Y117" s="6" t="n"/>
+      <c r="Z117" s="6" t="n"/>
+      <c r="AA117" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="17" t="inlineStr">
         <is>
           <t>LEGENDA</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" s="18" t="n"/>
-      <c r="D119" s="19" t="inlineStr">
+    <row r="120">
+      <c r="B120" s="18" t="n"/>
+      <c r="D120" s="19" t="inlineStr">
         <is>
           <t>Done (verde)</t>
         </is>
       </c>
-      <c r="F119" s="20" t="n"/>
-      <c r="G119" s="21" t="inlineStr">
+      <c r="F120" s="20" t="n"/>
+      <c r="G120" s="21" t="inlineStr">
         <is>
           <t>Track: Client/Pro → André  (esperienza cliente e professionista)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="22" t="n"/>
-      <c r="D120" s="19" t="inlineStr">
+    <row r="121">
+      <c r="B121" s="22" t="n"/>
+      <c r="D121" s="19" t="inlineStr">
         <is>
           <t>In progress (blu)</t>
         </is>
       </c>
-      <c r="F120" s="23" t="n"/>
-      <c r="G120" s="24" t="inlineStr">
+      <c r="F121" s="23" t="n"/>
+      <c r="G121" s="24" t="inlineStr">
         <is>
           <t>Track: Internal → Lucio  (dati, dashboard, admin, privacy)</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" s="25" t="n"/>
-      <c r="D121" s="19" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="25" t="n"/>
+      <c r="D122" s="19" t="inlineStr">
         <is>
           <t>Planned (grigio)</t>
         </is>
       </c>
-      <c r="F121" s="26" t="n"/>
-      <c r="G121" s="27" t="inlineStr">
+      <c r="F122" s="26" t="n"/>
+      <c r="G122" s="27" t="inlineStr">
         <is>
           <t>Track: Shared  (infra, legale, GTM, milestone)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="28" t="n"/>
-      <c r="D122" s="19" t="inlineStr">
+    <row r="123">
+      <c r="B123" s="28" t="n"/>
+      <c r="D123" s="19" t="inlineStr">
         <is>
           <t>Milestone / gate (ambra)</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="D124" s="29" t="inlineStr">
+    <row r="125">
+      <c r="D125" s="29" t="inlineStr">
         <is>
           <t>Fonte dati: roadmap.csv (modificalo e rilancia build_roadmap.py). Le barre si disegnano da Status+Start+End; 'Done on' = data di completamento effettiva. Mese corrente evidenziato in rosso. Email notifiche: pronte ma DORMIENTI fino al task 15.4.</t>
         </is>
       </c>
     </row>
-    <row r="125"/>
     <row r="126"/>
     <row r="127"/>
+    <row r="128"/>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D125:M128"/>
+    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A114:H114"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A109:H109"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A85:H85"/>
     <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A115:H115"/>
     <mergeCell ref="G121:M121"/>
-    <mergeCell ref="A108:H108"/>
-    <mergeCell ref="G119:M119"/>
+    <mergeCell ref="G122:M122"/>
     <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="D124:M127"/>
     <mergeCell ref="G120:M120"/>
   </mergeCells>
-  <conditionalFormatting sqref="I3:AA116">
+  <conditionalFormatting sqref="I3:AA117">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($F3&lt;&gt;"",I$2&lt;=$G3,EOMONTH(I$2,0)&gt;=$F3,$E3="Done")</formula>
     </cfRule>
